--- a/fhir/ValueSet-VentralHernieCicatriceTypeDHDB.xlsx
+++ b/fhir/ValueSet-VentralHernieCicatriceTypeDHDB.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.26.0</t>
+    <t>2.26.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-07-20T00:00:00+02:00</t>
+    <t>2026-09-26T00:00:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -106,7 +106,13 @@
     <t>cross_cicatrice</t>
   </si>
   <si>
-    <t>Tværcicatrice Port-hernie</t>
+    <t>Tværcicatrice</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>Port-hernie</t>
   </si>
   <si>
     <t>System URI</t>
@@ -383,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -416,18 +422,26 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -454,10 +468,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -470,10 +484,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
